--- a/artfynd/A 3383-2025 artfynd.xlsx
+++ b/artfynd/A 3383-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65711274</v>
       </c>
       <c r="B2" t="n">
-        <v>56364</v>
+        <v>57445</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551905.262174548</v>
+        <v>551905</v>
       </c>
       <c r="R2" t="n">
-        <v>6919587.157436547</v>
+        <v>6919587</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,19 +759,9 @@
           <t>2017-05-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-05-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 3383-2025 artfynd.xlsx
+++ b/artfynd/A 3383-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65711274</v>
       </c>
       <c r="B2" t="n">
-        <v>57445</v>
+        <v>57448</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 3383-2025 artfynd.xlsx
+++ b/artfynd/A 3383-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65711274</v>
       </c>
       <c r="B2" t="n">
-        <v>57448</v>
+        <v>57454</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
